--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_m_movinterna_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_m_movinterna_a_2021_nacional.xlsx
@@ -28,19 +28,19 @@
     <t xml:space="preserve">Valor</t>
   </si>
   <si>
+    <t xml:space="preserve">Hombres</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 06:57</t>
+    <t xml:space="preserve">2026-09-08 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,7 +474,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5.65</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6.88</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="4">
@@ -496,7 +496,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7.97</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7.79</v>
+        <v>9.62</v>
       </c>
     </row>
     <row r="6">
@@ -518,7 +518,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7.43</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="7">
@@ -529,7 +529,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7.78</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="8">
@@ -540,7 +540,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6.09</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="9">
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7.74</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="10">
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>10.25</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +573,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>9.62</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9.82</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="13">
@@ -595,7 +595,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10.43</v>
+        <v>7.78</v>
       </c>
     </row>
   </sheetData>
